--- a/E/DU2BMKT.xlsx
+++ b/E/DU2BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t/>
   </si>
   <si>
-    <t>20140801</t>
-  </si>
-  <si>
-    <t>IDM TISU ROL 8'S</t>
+    <t>20070712</t>
+  </si>
+  <si>
+    <t>MERRIES PANT GS28 L</t>
   </si>
   <si>
     <t>DU2BMKT</t>
@@ -28,7 +28,28 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT</t>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20113567</t>
+  </si>
+  <si>
+    <t>GENTLE GEN MR.BRZ700</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20115959</t>
+  </si>
+  <si>
+    <t>GENTLE GEN FR.PE 700</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
 </sst>
 </file>
@@ -421,13 +442,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="4" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -468,6 +489,46 @@
       </c>
       <c r="F2" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU2BMKT.xlsx
+++ b/E/DU2BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t/>
   </si>
   <si>
-    <t>20070712</t>
-  </si>
-  <si>
-    <t>MERRIES PANT GS28 L</t>
+    <t>20098001</t>
+  </si>
+  <si>
+    <t>GENKI MOKO2 26+2S XL</t>
   </si>
   <si>
     <t>DU2BMKT</t>
@@ -28,28 +28,19 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20113567</t>
-  </si>
-  <si>
-    <t>GENTLE GEN MR.BRZ700</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20140801</t>
+  </si>
+  <si>
+    <t>IDM TISU ROL 8'S</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20115959</t>
-  </si>
-  <si>
-    <t>GENTLE GEN FR.PE 700</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>PT</t>
   </si>
 </sst>
 </file>
@@ -442,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -511,26 +502,6 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/DU2BMKT.xlsx
+++ b/E/DU2BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
   <si>
     <t/>
   </si>
   <si>
-    <t>20098001</t>
-  </si>
-  <si>
-    <t>GENKI MOKO2 26+2S XL</t>
+    <t>20137024</t>
+  </si>
+  <si>
+    <t>SWEETY X-PRT M-44</t>
   </si>
   <si>
     <t>DU2BMKT</t>
@@ -31,16 +31,13 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20140801</t>
-  </si>
-  <si>
-    <t>IDM TISU ROL 8'S</t>
+    <t>20137023</t>
+  </si>
+  <si>
+    <t>SWEETY X-PERT L-38</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>PT</t>
   </si>
 </sst>
 </file>
@@ -437,7 +434,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
@@ -499,7 +496,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU2BMKT.xlsx
+++ b/E/DU2BMKT.xlsx
@@ -16,10 +16,10 @@
     <t/>
   </si>
   <si>
-    <t>20137024</t>
-  </si>
-  <si>
-    <t>SWEETY X-PRT M-44</t>
+    <t>20130078</t>
+  </si>
+  <si>
+    <t>BABY HP PNKFONG L-28</t>
   </si>
   <si>
     <t>DU2BMKT</t>
@@ -28,13 +28,13 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20137023</t>
-  </si>
-  <si>
-    <t>SWEETY X-PERT L-38</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20073499</t>
+  </si>
+  <si>
+    <t>SO KLN MGNL&amp;BRY 720G</t>
   </si>
   <si>
     <t>2</t>
@@ -434,7 +434,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>

--- a/E/DU2BMKT.xlsx
+++ b/E/DU2BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
   <si>
     <t/>
   </si>
   <si>
-    <t>20130078</t>
-  </si>
-  <si>
-    <t>BABY HP PNKFONG L-28</t>
+    <t>20069549</t>
+  </si>
+  <si>
+    <t>IDM DIAPER ADULT 6XL</t>
   </si>
   <si>
     <t>DU2BMKT</t>
@@ -28,16 +28,31 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20092331</t>
+  </si>
+  <si>
+    <t>EKONOMI LIQ JR.NP650</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20073499</t>
-  </si>
-  <si>
-    <t>SO KLN MGNL&amp;BRY 720G</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>20136124</t>
+  </si>
+  <si>
+    <t>EKNOMI LIQ N&amp;JN 675G</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
   </si>
 </sst>
 </file>
@@ -430,13 +445,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -496,7 +511,27 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU2BMKT.xlsx
+++ b/E/DU2BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t/>
   </si>
   <si>
-    <t>20069549</t>
-  </si>
-  <si>
-    <t>IDM DIAPER ADULT 6XL</t>
+    <t>20139653</t>
+  </si>
+  <si>
+    <t>LRST FAC.TIS 2X200S</t>
   </si>
   <si>
     <t>DU2BMKT</t>
@@ -28,13 +28,13 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20092331</t>
-  </si>
-  <si>
-    <t>EKONOMI LIQ JR.NP650</t>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20081448</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT H.SM 600</t>
   </si>
   <si>
     <t>2</t>
@@ -43,16 +43,13 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20136124</t>
-  </si>
-  <si>
-    <t>EKNOMI LIQ N&amp;JN 675G</t>
+    <t>20081449</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT P.DW 600</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
   </si>
 </sst>
 </file>
@@ -451,7 +448,7 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -531,7 +528,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU2BMKT.xlsx
+++ b/E/DU2BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
   <si>
     <t/>
   </si>
   <si>
-    <t>20139653</t>
-  </si>
-  <si>
-    <t>LRST FAC.TIS 2X200S</t>
+    <t>20070711</t>
+  </si>
+  <si>
+    <t>MERRIES PANT GS32 M</t>
   </si>
   <si>
     <t>DU2BMKT</t>
@@ -28,28 +28,16 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20081448</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT H.SM 600</t>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20070712</t>
+  </si>
+  <si>
+    <t>MERRIES PANT GS28 L</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20081449</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT P.DW 600</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -442,13 +430,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -508,27 +496,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU2BMKT.xlsx
+++ b/E/DU2BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
   <si>
     <t/>
   </si>
   <si>
-    <t>20070711</t>
-  </si>
-  <si>
-    <t>MERRIES PANT GS32 M</t>
+    <t>20021324</t>
+  </si>
+  <si>
+    <t>LAURIER RLX NG 12/35</t>
   </si>
   <si>
     <t>DU2BMKT</t>
@@ -31,13 +31,37 @@
     <t>RT</t>
   </si>
   <si>
-    <t>20070712</t>
-  </si>
-  <si>
-    <t>MERRIES PANT GS28 L</t>
+    <t>20039728</t>
+  </si>
+  <si>
+    <t>SHINZU'I KIREI 380ML</t>
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20130653</t>
+  </si>
+  <si>
+    <t>SHINZU'I SKURA 380ML</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20009500</t>
+  </si>
+  <si>
+    <t>BIORE B.FOAM RELX400</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
 </sst>
 </file>
@@ -430,13 +454,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="4" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -496,7 +520,47 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU2BMKT.xlsx
+++ b/E/DU2BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t/>
   </si>
   <si>
-    <t>20021324</t>
-  </si>
-  <si>
-    <t>LAURIER RLX NG 12/35</t>
+    <t>20070711</t>
+  </si>
+  <si>
+    <t>MERRIES PANT GS32 M</t>
   </si>
   <si>
     <t>DU2BMKT</t>
@@ -31,37 +31,16 @@
     <t>RT</t>
   </si>
   <si>
-    <t>20039728</t>
-  </si>
-  <si>
-    <t>SHINZU'I KIREI 380ML</t>
+    <t>20069547</t>
+  </si>
+  <si>
+    <t>IDM DIAPER ADULT 7L</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20130653</t>
-  </si>
-  <si>
-    <t>SHINZU'I SKURA 380ML</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20009500</t>
-  </si>
-  <si>
-    <t>BIORE B.FOAM RELX400</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -454,11 +433,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
@@ -523,46 +502,6 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/DU2BMKT.xlsx
+++ b/E/DU2BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
   <si>
     <t/>
   </si>
   <si>
-    <t>20070711</t>
-  </si>
-  <si>
-    <t>MERRIES PANT GS32 M</t>
+    <t>20098001</t>
+  </si>
+  <si>
+    <t>GENKI MOKO2 26+2S XL</t>
   </si>
   <si>
     <t>DU2BMKT</t>
@@ -28,19 +28,16 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20069547</t>
-  </si>
-  <si>
-    <t>IDM DIAPER ADULT 7L</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20098000</t>
+  </si>
+  <si>
+    <t>GENKI MOKO2 28+2S L</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
   </si>
 </sst>
 </file>
@@ -437,7 +434,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
@@ -499,7 +496,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU2BMKT.xlsx
+++ b/E/DU2BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
   <si>
     <t/>
   </si>
   <si>
-    <t>20098001</t>
-  </si>
-  <si>
-    <t>GENKI MOKO2 26+2S XL</t>
+    <t>20005584</t>
+  </si>
+  <si>
+    <t>ZWTSL B/BTH HB AV400</t>
   </si>
   <si>
     <t>DU2BMKT</t>
@@ -28,16 +28,37 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20098000</t>
-  </si>
-  <si>
-    <t>GENKI MOKO2 28+2S L</t>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20039728</t>
+  </si>
+  <si>
+    <t>SHINZU'I KIREI 380ML</t>
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20039727</t>
+  </si>
+  <si>
+    <t>SHINZU'I MATSU 380ML</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20081452</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW RED 800</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
 </sst>
 </file>
@@ -430,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -496,6 +517,46 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/DU2BMKT.xlsx
+++ b/E/DU2BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t/>
   </si>
   <si>
-    <t>20005584</t>
-  </si>
-  <si>
-    <t>ZWTSL B/BTH HB AV400</t>
+    <t>20106045</t>
+  </si>
+  <si>
+    <t>CAT CHOIZE+ T&amp;S 500G</t>
   </si>
   <si>
     <t>DU2BMKT</t>
@@ -28,37 +28,19 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20039728</t>
-  </si>
-  <si>
-    <t>SHINZU'I KIREI 380ML</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20021324</t>
+  </si>
+  <si>
+    <t>LAURIER RLX NG 12/35</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20039727</t>
-  </si>
-  <si>
-    <t>SHINZU'I MATSU 380ML</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20081452</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW RED 800</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>RT</t>
   </si>
 </sst>
 </file>
@@ -451,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -520,46 +502,6 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/DU2BMKT.xlsx
+++ b/E/DU2BMKT.xlsx
@@ -16,10 +16,10 @@
     <t/>
   </si>
   <si>
-    <t>20106045</t>
-  </si>
-  <si>
-    <t>CAT CHOIZE+ T&amp;S 500G</t>
+    <t>20048847</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP900</t>
   </si>
   <si>
     <t>DU2BMKT</t>
@@ -28,13 +28,13 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20021324</t>
-  </si>
-  <si>
-    <t>LAURIER RLX NG 12/35</t>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20070711</t>
+  </si>
+  <si>
+    <t>MERRIES PANT GS32 M</t>
   </si>
   <si>
     <t>2</t>
@@ -439,7 +439,7 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">

--- a/E/DU2BMKT.xlsx
+++ b/E/DU2BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="21">
   <si>
     <t/>
   </si>
   <si>
-    <t>20048847</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP900</t>
+    <t>20047284</t>
+  </si>
+  <si>
+    <t>CHARM N WG 12 35 CM</t>
   </si>
   <si>
     <t>DU2BMKT</t>
@@ -31,16 +31,49 @@
     <t>PT</t>
   </si>
   <si>
-    <t>20070711</t>
-  </si>
-  <si>
-    <t>MERRIES PANT GS32 M</t>
+    <t>20140420</t>
+  </si>
+  <si>
+    <t>CHARM N DS 11S 35 CM</t>
+  </si>
+  <si>
+    <t>20140429</t>
+  </si>
+  <si>
+    <t>CHARM N DS 17 29 CM</t>
+  </si>
+  <si>
+    <t>20071105</t>
+  </si>
+  <si>
+    <t>MIT TIS. PF 2x50'S</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT</t>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>10004067</t>
+  </si>
+  <si>
+    <t>M/LMN PCH LMN 690 G</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20034450</t>
+  </si>
+  <si>
+    <t>M/LMN JRK NPS 690 G</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
 </sst>
 </file>
@@ -433,13 +466,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="4" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -496,10 +529,90 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU2BMKT.xlsx
+++ b/E/DU2BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
   <si>
     <t/>
   </si>
   <si>
-    <t>20047284</t>
-  </si>
-  <si>
-    <t>CHARM N WG 12 35 CM</t>
+    <t>20141206</t>
+  </si>
+  <si>
+    <t>LARISST M.W WIPE 8X8</t>
   </si>
   <si>
     <t>DU2BMKT</t>
@@ -28,25 +28,13 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20140420</t>
-  </si>
-  <si>
-    <t>CHARM N DS 11S 35 CM</t>
-  </si>
-  <si>
-    <t>20140429</t>
-  </si>
-  <si>
-    <t>CHARM N DS 17 29 CM</t>
+    <t>RT</t>
   </si>
   <si>
     <t>20071105</t>
   </si>
   <si>
-    <t>MIT TIS. PF 2x50'S</t>
+    <t>MITU GP PURPLE 2X50S</t>
   </si>
   <si>
     <t>2</t>
@@ -55,25 +43,25 @@
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>10004067</t>
-  </si>
-  <si>
-    <t>M/LMN PCH LMN 690 G</t>
+    <t>20001061</t>
+  </si>
+  <si>
+    <t>MITU G/P PINK 2X50'S</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20034450</t>
-  </si>
-  <si>
-    <t>M/LMN JRK NPS 690 G</t>
+    <t>20073425</t>
+  </si>
+  <si>
+    <t>IDM P.PRNG JRK.N 650</t>
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
   </si>
 </sst>
 </file>
@@ -466,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -529,18 +517,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -549,18 +537,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -569,50 +557,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU2BMKT.xlsx
+++ b/E/DU2BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t/>
   </si>
   <si>
-    <t>20141206</t>
-  </si>
-  <si>
-    <t>LARISST M.W WIPE 8X8</t>
+    <t>20021324</t>
+  </si>
+  <si>
+    <t>LAURIER RLX NG 12/35</t>
   </si>
   <si>
     <t>DU2BMKT</t>
@@ -31,37 +31,25 @@
     <t>RT</t>
   </si>
   <si>
-    <t>20071105</t>
-  </si>
-  <si>
-    <t>MITU GP PURPLE 2X50S</t>
+    <t>10012548</t>
+  </si>
+  <si>
+    <t>SOKLIN RLX/LAV RF770</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20001061</t>
-  </si>
-  <si>
-    <t>MITU G/P PINK 2X50'S</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20093627</t>
+  </si>
+  <si>
+    <t>SOKLN LIQ SAKURA 510</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>20073425</t>
-  </si>
-  <si>
-    <t>IDM P.PRNG JRK.N 650</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
   </si>
 </sst>
 </file>
@@ -454,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -543,26 +531,6 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/DU2BMKT.xlsx
+++ b/E/DU2BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
   <si>
     <t/>
   </si>
   <si>
-    <t>20021324</t>
-  </si>
-  <si>
-    <t>LAURIER RLX NG 12/35</t>
+    <t>20106045</t>
+  </si>
+  <si>
+    <t>CAT CHOIZE+ T&amp;S 500G</t>
   </si>
   <si>
     <t>DU2BMKT</t>
@@ -28,28 +28,31 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20070711</t>
+  </si>
+  <si>
+    <t>MERRIES PANT GS32 M</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT</t>
   </si>
   <si>
-    <t>10012548</t>
-  </si>
-  <si>
-    <t>SOKLIN RLX/LAV RF770</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20093627</t>
-  </si>
-  <si>
-    <t>SOKLN LIQ SAKURA 510</t>
+    <t>10005482</t>
+  </si>
+  <si>
+    <t>SNLIGHT LIME PCH 660</t>
   </si>
   <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>PT</t>
   </si>
 </sst>
 </file>
@@ -442,16 +445,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -470,8 +474,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -487,11 +497,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -507,11 +517,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -527,8 +537,8 @@
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
+      <c r="H4" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU2BMKT.xlsx
+++ b/E/DU2BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t/>
   </si>
   <si>
-    <t>20106045</t>
-  </si>
-  <si>
-    <t>CAT CHOIZE+ T&amp;S 500G</t>
+    <t>20069547</t>
+  </si>
+  <si>
+    <t>IDM DIAPER ADULT 7L</t>
   </si>
   <si>
     <t>DU2BMKT</t>
@@ -31,28 +31,25 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20070711</t>
-  </si>
-  <si>
-    <t>MERRIES PANT GS32 M</t>
+    <t>20137024</t>
+  </si>
+  <si>
+    <t>SWEETY X-PRT M-44</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>10005482</t>
-  </si>
-  <si>
-    <t>SNLIGHT LIME PCH 660</t>
+    <t>20034450</t>
+  </si>
+  <si>
+    <t>MAMA/L JERUK NPS 650</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>PT</t>
+    <t>RT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -445,17 +442,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -474,14 +470,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -497,11 +487,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -517,16 +507,16 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -535,10 +525,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU2BMKT.xlsx
+++ b/E/DU2BMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
   <si>
     <t/>
   </si>
   <si>
-    <t>20069547</t>
-  </si>
-  <si>
-    <t>IDM DIAPER ADULT 7L</t>
+    <t>20141206</t>
+  </si>
+  <si>
+    <t>LARISST M.W WIPE 8X8</t>
   </si>
   <si>
     <t>DU2BMKT</t>
@@ -28,28 +28,37 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20137024</t>
-  </si>
-  <si>
-    <t>SWEETY X-PRT M-44</t>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>10005482</t>
+  </si>
+  <si>
+    <t>SNLIGHT LIME PCH 660</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20034450</t>
-  </si>
-  <si>
-    <t>MAMA/L JERUK NPS 650</t>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20090067</t>
+  </si>
+  <si>
+    <t>SNLGHT MINT A.BAU600</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
+    <t>20135144</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO NATURE600</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
 </sst>
 </file>
@@ -442,13 +451,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -508,15 +517,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -525,10 +534,30 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU2BMKT.xlsx
+++ b/E/DU2BMKT.xlsx
@@ -16,10 +16,10 @@
     <t/>
   </si>
   <si>
-    <t>20141206</t>
-  </si>
-  <si>
-    <t>LARISST M.W WIPE 8X8</t>
+    <t>20098000</t>
+  </si>
+  <si>
+    <t>GENKI MOKO2 28+2S L</t>
   </si>
   <si>
     <t>DU2BMKT</t>
@@ -28,37 +28,37 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>10005482</t>
-  </si>
-  <si>
-    <t>SNLIGHT LIME PCH 660</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20098001</t>
+  </si>
+  <si>
+    <t>GENKI MOKO2 26+2S XL</t>
+  </si>
+  <si>
+    <t>20092331</t>
+  </si>
+  <si>
+    <t>EKONOMI LIQ JR.NP675</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20090067</t>
-  </si>
-  <si>
-    <t>SNLGHT MINT A.BAU600</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20136124</t>
+  </si>
+  <si>
+    <t>EKNOMI LIQ N&amp;JN 675G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20135144</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO NATURE600</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>RT,(E-1.5B)</t>
   </si>
 </sst>
 </file>
@@ -457,7 +457,7 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="4" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -514,18 +514,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -534,18 +534,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -554,10 +554,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU2BMKT.xlsx
+++ b/E/DU2BMKT.xlsx
@@ -16,10 +16,10 @@
     <t/>
   </si>
   <si>
-    <t>20114021</t>
-  </si>
-  <si>
-    <t>IDM TISU WJH PRM 100</t>
+    <t>20131668</t>
+  </si>
+  <si>
+    <t>IDM FAC.COTTON 50G</t>
   </si>
   <si>
     <t>DU2BMKT</t>
@@ -28,28 +28,28 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10005482</t>
+  </si>
+  <si>
+    <t>SNLGHT LME PCH 660 G</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>PT</t>
   </si>
   <si>
-    <t>20054750</t>
-  </si>
-  <si>
-    <t>RNSO LIQ PRFM 510 G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20137793</t>
-  </si>
-  <si>
-    <t>RNSO ROSE FRS 510 G</t>
+    <t>20090067</t>
+  </si>
+  <si>
+    <t>SNLGHT M A.BAU 600 G</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -508,15 +508,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -525,10 +525,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
